--- a/nomination_forms/017_nomination_for_judicial_positions--nomination_forms.xlsx
+++ b/nomination_forms/017_nomination_for_judicial_positions--nomination_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,13 +515,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nomination_details</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Nominee's Name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please enter your name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -538,13 +542,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nomination_nominator</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Nominator's Name</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please enter the name of the person nominating this judicial officer</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -561,17 +569,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nominee_name</t>
+          <t>Nominee Name</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Enter Nominee's Full Name</t>
+          <t>Please enter the nominee's full name</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -588,17 +596,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nominee_address</t>
+          <t>Nominee's Mailing Address</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Enter Nominee's Mailing Address</t>
+          <t>Please enter the nominee's mailing address</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -615,13 +623,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nominee_phone</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Nominee's Phone Number</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please enter the nominee's phone number</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -638,13 +650,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nominee_email</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Nominee's Email</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please enter the nominee's email</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -661,13 +677,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nomination_reason</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Nomination Reason</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please enter a brief description of why the nominee is being nominated</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -684,13 +704,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>supporting_documents</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Supporting Documents</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please attach relevant supporting documents</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -707,17 +731,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nominee_judicial_qualifications</t>
+          <t>Nominee's Judicial Qualifications</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Enter nominee's judicial Qualifications</t>
+          <t>Please list the nominee's judicial qualifications</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -734,13 +758,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nomination_date</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Nomination Date</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please enter the date of nomination</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -757,13 +785,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nomination_status</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Nomination Status</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please enter the current status of the nomination</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -780,13 +812,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nomination_comments</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please enter any additional comments</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -798,18 +834,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nomination_organizer</t>
+          <t>nomination_organiser</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nomination_organizer</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Nomination Organiser</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please enter the name of the person organising this nomination</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -821,18 +861,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nomination_location</t>
+          <t>nomination_organiser_phone</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nomination_location</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Nomination Organiser Contact Number</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please enter the nominee organiser's contact number</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -844,18 +888,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nomination_organizer_email</t>
+          <t>nomination_organiser_email</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>nomination_organizer_email</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Nomination Organiser Email</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please enter the nominee organiser's email</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -867,18 +915,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nomination_organizer_phone</t>
+          <t>nomination_location</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nomination_organizer_phone</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Nomination Location</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please enter the location of the nomination</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -890,18 +942,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nomination_organizer_address</t>
+          <t>nominee_judicial_experience</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>nomination_organizer_address</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Nominee's Judicial Experience</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please enter the nominee's judicial experience</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -913,248 +969,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nominee_judicial_experience</t>
+          <t>nominee_bar_number</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>nominee_judicial_experience</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Nominee's Bar Number</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please enter the nominee's bar number</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>nominee_bar_number</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>nominee_bar_number</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>nomination_judiciary</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>nomination_judiciary</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>nomination_county</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>nomination_county</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>nomination_state</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>nomination_state</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>nomination_city</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>nomination_city</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>nomination_zip</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>nomination_zip</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>nomination_comments</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>nomination_comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>nomination_nominator_id</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>nomination_nominator</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>nominee_bar_number</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>nominee_bar_number</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>nomination_nominator_email</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>nomination_nominator_email</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
